--- a/AdditionalData/Tables/Height just before changes in thickness thickness.xlsx
+++ b/AdditionalData/Tables/Height just before changes in thickness thickness.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="te paso una nueva lista de rang" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
